--- a/StructureDefinition-statim.xlsx
+++ b/StructureDefinition-statim.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T00:29:47+00:00</t>
+    <t>2026-04-17T06:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-statim.xlsx
+++ b/StructureDefinition-statim.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T06:29:04+00:00</t>
+    <t>2026-04-24T01:18:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-statim.xlsx
+++ b/StructureDefinition-statim.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T01:18:12+00:00</t>
+    <t>2026-06-24T20:43:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
